--- a/docs/files/REPORT_FILTRI/Agente - CR CASCIARI PAOLO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CASCIARI PAOLO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N11" headerRowCount="1">
-  <autoFilter ref="A10:N11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N12" headerRowCount="1">
+  <autoFilter ref="A10:N12"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -817,35 +817,85 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11295</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>MONTIGNOSO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CASCIARI PAOLO</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" s="12" t="n">
+      <c r="G12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
+      <c r="M12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - CR CASCIARI PAOLO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CASCIARI PAOLO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -841,7 +841,7 @@
         <v>16</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>3</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - CR CASCIARI PAOLO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR CASCIARI PAOLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>33</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
@@ -838,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
@@ -885,17 +885,17 @@
         <v>1</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
